--- a/payment_forms/036_paypal_nonprofit_donation_form--payment_forms.xlsx
+++ b/payment_forms/036_paypal_nonprofit_donation_form--payment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -828,7 +828,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Donor Name</t>
+          <t>Form Donor Name</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -851,7 +851,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Donor Email</t>
+          <t>Form Donor Email</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -874,7 +874,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Donation Amount</t>
+          <t>Form Donation Amount</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -897,7 +897,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Donor Phone</t>
+          <t>Form Donor Phone</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -920,7 +920,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Donation Frequency</t>
+          <t>Form Donation Frequency</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -943,7 +943,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Payment Method</t>
+          <t>Form Payment Method</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -966,7 +966,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Comment</t>
+          <t>Form Comment</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Form Date</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1035,7 +1035,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Time</t>
+          <t>Form Time</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1053,12 +1053,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>form_submit</t>
+          <t>form_submit_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Submit</t>
+          <t>Form Submit 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
